--- a/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
+++ b/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603</t>
+          <t xml:space="preserve">605</t>
         </is>
       </c>
     </row>
@@ -102,7 +102,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
@@ -114,7 +114,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
     </row>
@@ -138,7 +138,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
     </row>
@@ -150,7 +150,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
     </row>
@@ -162,7 +162,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
     </row>
@@ -4034,47 +4034,47 @@
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4084,24 +4084,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Local PlantControlV2 exact equation and supplemental RAW observations; data/current_v8/st_power_evidence_20260924.json</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4228,79 +4228,146 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
 </worksheet>
 </file>
 
@@ -5467,8 +5534,40 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-036</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F37"/>
 </worksheet>
 </file>
 
@@ -7981,98 +8080,145 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I7"/>
 </worksheet>
 </file>
--- a/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
+++ b/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603</t>
+          <t xml:space="preserve">604</t>
         </is>
       </c>
     </row>
@@ -102,7 +102,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
@@ -114,7 +114,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
     </row>
@@ -138,7 +138,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
     </row>
@@ -150,7 +150,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
@@ -162,7 +162,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
     </row>
@@ -4034,47 +4034,47 @@
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4084,24 +4084,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Exact Modelica equation + private local RAW readback hash; behavior verification remains PARTIAL</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4228,79 +4228,146 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
 </worksheet>
 </file>
 
@@ -5467,8 +5534,40 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-036</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F37"/>
 </worksheet>
 </file>
 
@@ -7981,98 +8080,145 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I7"/>
 </worksheet>
 </file>
--- a/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
+++ b/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
@@ -90,96 +90,168 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">live_tags</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_groups</t>
+          <t xml:space="preserve">searchable_tags</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">605</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">equipment_pages</t>
+          <t xml:space="preserve">model_source_raw_observed_tags</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pages</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_inputs</t>
+          <t xml:space="preserve">live_rules</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_outputs</t>
+          <t xml:space="preserve">source_mapped_rules</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">input_groups</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">live_input_groups</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equipment_pages</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pages</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_inputs</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_outputs</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">derived_outputs</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>
 
@@ -679,6 +751,15 @@
     <col min="11" max="11" width="38" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="38" customWidth="1"/>
+    <col min="15" max="15" width="38" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -747,6 +828,51 @@
           <t xml:space="preserve">source_basis</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_mapped</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runtime_inclusion</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model_source_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_session_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_rows</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_closed_samples</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_open_samples</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open_behavior_test_status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -814,6 +940,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -881,6 +1052,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -948,6 +1164,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1015,6 +1276,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1082,6 +1388,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1149,6 +1500,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1216,6 +1612,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1283,6 +1724,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1350,6 +1836,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1417,6 +1948,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1484,6 +2060,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1551,6 +2172,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1618,6 +2284,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1685,6 +2396,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1752,6 +2508,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1819,6 +2620,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1886,6 +2732,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1953,6 +2844,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2020,6 +2956,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2087,6 +3068,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2154,6 +3180,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2221,6 +3292,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2288,6 +3404,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2355,6 +3516,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2422,6 +3628,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2489,6 +3740,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2556,6 +3852,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2623,6 +3964,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2690,6 +4076,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2757,6 +4188,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2824,6 +4300,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2891,6 +4412,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2958,6 +4524,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3025,6 +4636,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3092,6 +4748,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3159,6 +4860,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3226,6 +4972,51 @@
           <t xml:space="preserve">Exact expression recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -3293,6 +5084,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -3360,6 +5196,51 @@
           <t xml:space="preserve">Exact GT request equation recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -3427,6 +5308,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3494,6 +5420,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3561,6 +5532,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3628,6 +5644,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3695,6 +5756,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3762,6 +5868,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -3829,6 +5980,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -3896,6 +6092,51 @@
           <t xml:space="preserve">9-cause common-trip matrix + RAW nodes</t>
         </is>
       </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -3963,6 +6204,51 @@
           <t xml:space="preserve">Exact model equation</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -4030,6 +6316,51 @@
           <t xml:space="preserve">Exact model equation</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -4054,12 +6385,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW | vpp52STClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4094,7 +6425,52 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local PlantControlV2 exact equation and supplemental RAW observations; data/current_v8/st_power_evidence_20260924.json</t>
+          <t xml:space="preserve">Model source modelica/TripLens_CombinedCycle_TripTAC_ProcessView_v36.mo lines 1136-1137 (cd454995656af9a8747efe8930d2aa0b92f98e1083acadc858eaa7959ea6d2c5); RAW RAW_SESSION_20260924_191347.csv (055f8a21b8f586feafaa6fe6705cfca05b4f1e833713991a0cac1f0e94ad6fd9).</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_SESSION_OBSERVED_CLOSED_ONLY</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_TESTED</t>
         </is>
       </c>
     </row>
@@ -4164,6 +6540,51 @@
           <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -4231,6 +6652,51 @@
           <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
         </is>
       </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4298,6 +6764,51 @@
           <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -4365,9 +6876,54 @@
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:V55"/>
 </worksheet>
 </file>
 
@@ -8080,79 +10636,79 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-036</t>
+          <t xml:space="preserve">IG-028</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST grid power response after 52ST opens</t>
+          <t xml:space="preserve">52ST breaker open timing</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">immediate model relation</t>
+          <t xml:space="preserve">0.100 s</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">follows 52ST closed feedback</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTGridPowerMW</t>
+          <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-027</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0 s</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8162,7 +10718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8171,54 +10727,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IG-027</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52ST trip command</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST latch active</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 s</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpp52STTripCmd</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:I6"/>
 </worksheet>
 </file>
--- a/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
+++ b/generated/logic/10_OPERATIONAL_LOGIC_GROUP_CURRENT_V8.xlsx
@@ -90,96 +90,168 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">604</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">live_tags</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_groups</t>
+          <t xml:space="preserve">searchable_tags</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">606</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">equipment_pages</t>
+          <t xml:space="preserve">model_source_raw_observed_tags</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pages</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_inputs</t>
+          <t xml:space="preserve">live_rules</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">native_outputs</t>
+          <t xml:space="preserve">source_mapped_rules</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">input_groups</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">live_input_groups</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">equipment_pages</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pages</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_inputs</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">native_outputs</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">derived_outputs</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>
 
@@ -679,6 +751,15 @@
     <col min="11" max="11" width="38" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="38" customWidth="1"/>
+    <col min="15" max="15" width="38" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -747,6 +828,51 @@
           <t xml:space="preserve">source_basis</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_kind</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_mapped</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runtime_inclusion</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model_source_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_session_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_rows</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_closed_samples</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">raw_open_samples</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open_behavior_test_status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -814,6 +940,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -881,6 +1052,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -948,6 +1164,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1015,6 +1276,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1082,6 +1388,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1149,6 +1500,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1216,6 +1612,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1283,6 +1724,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1350,6 +1836,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1417,6 +1948,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1484,6 +2060,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1551,6 +2172,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1618,6 +2284,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1685,6 +2396,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1752,6 +2508,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1819,6 +2620,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1886,6 +2732,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1953,6 +2844,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2020,6 +2956,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2087,6 +3068,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2154,6 +3180,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2221,6 +3292,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW node is vpp*TurbineSteamFlowTH; threshold converted exactly from kg/s × 3.6</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2288,6 +3404,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2355,6 +3516,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2422,6 +3628,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2489,6 +3740,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2556,6 +3852,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2623,6 +3964,51 @@
           <t xml:space="preserve">Current DCS alarm rule; RAW input node exists</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2690,6 +4076,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2757,6 +4188,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2824,6 +4300,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2891,6 +4412,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2958,6 +4524,51 @@
           <t xml:space="preserve">Reset node exists in RAW; exact reset sequencing remains runtime-owned</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3025,6 +4636,51 @@
           <t xml:space="preserve">All command/latch/breaker nodes exist in RAW; exact client-side sequencing is not re-invented here</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3092,6 +4748,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3159,6 +4860,51 @@
           <t xml:space="preserve">RAW node + runtime regression evidence</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3226,6 +4972,51 @@
           <t xml:space="preserve">Exact expression recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -3293,6 +5084,51 @@
           <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -3360,6 +5196,51 @@
           <t xml:space="preserve">Exact GT request equation recovered from model compile trace</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -3427,6 +5308,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3494,6 +5420,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3561,6 +5532,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3628,6 +5644,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3695,6 +5756,51 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3762,11 +5868,56 @@
           <t xml:space="preserve">RAW comparator/cause nodes exist; exact internal debounce retained in runtime</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-LATCH</t>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3776,22 +5927,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST trip latch</t>
+          <t xml:space="preserve">52ST breaker open protection cause</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LATCH</t>
+          <t xml:space="preserve">PROTECTION_CAUSE</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest | vppSTTripResetNative</t>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
+          <t xml:space="preserve">52ST close command &lt; 0.5 -&gt; breaker-open cause latch</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3801,12 +5952,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reset input</t>
+          <t xml:space="preserve">ST reset with active trip causes clear and 52ST command open</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
+          <t xml:space="preserve">vppCauseSTBreakerOpenWhileRunning</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3816,7 +5967,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-024</t>
+          <t xml:space="preserve">IG-037</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3826,14 +5977,59 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
+          <t xml:space="preserve">TRIPLENS_ST_BREAKER_OPEN_TRIP_V1; 2026-09-26 PlantControlV2 build 104046 runtime proof</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_RUNTIME_VERIFIED</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUNTIME_VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROT-ST-REQUEST</t>
+          <t xml:space="preserve">PROT-ST-LATCH</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3843,37 +6039,37 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST trip request common-trip matrix</t>
+          <t xml:space="preserve">ST trip latch</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRIP_REQUEST</t>
+          <t xml:space="preserve">LATCH</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseDirectGTTrip | vppCauseDirectSTTrip | vppCauseGTBreakerOpenWhileRunning | vppCauseHPDrumHH | vppCauseIPDrumHH | vppCauseLPDrumHH | vppCauseHPDrumLL | vppCauseIPDrumLL | vppCauseLPDrumLL</t>
+          <t xml:space="preserve">vppSTTripRequest | vppSTTripResetNative</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OR(all 9 causes)</t>
+          <t xml:space="preserve">request=1 AND reset&lt;0.5 -&gt; latch; reset clears</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 s</t>
+          <t xml:space="preserve">event-driven</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST reset</t>
+          <t xml:space="preserve">reset input</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripRequest</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3883,7 +6079,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-022</t>
+          <t xml:space="preserve">IG-024</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -3893,54 +6089,99 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-cause common-trip matrix + RAW nodes</t>
+          <t xml:space="preserve">Runtime latch node and request/reset nodes exist</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-POWER</t>
+          <t xml:space="preserve">PROT-ST-REQUEST</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Response</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT power response after breaker open</t>
+          <t xml:space="preserve">ST trip request</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
+          <t xml:space="preserve">TRIP_REQUEST</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppGTTripRequest | vppCauseDirectSTTrip | vppCauseSTBreakerOpenWhileRunning | vppCauseHPDrumHH | vppCauseIPDrumHH | vppCauseLPDrumHH</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
+          <t xml:space="preserve">OR(registered ST trip inputs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">immediate model relation</t>
+          <t xml:space="preserve">0 s</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">ST reset</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGPowerMW</t>
+          <t xml:space="preserve">vppSTTripRequest</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3950,7 +6191,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-029</t>
+          <t xml:space="preserve">IG-022</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -3960,14 +6201,59 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exact model equation</t>
+          <t xml:space="preserve">Current PlantControlV2 ST request equation; cause-count wording retired; 52ST breaker-open cause included.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-GT-SPEED</t>
+          <t xml:space="preserve">RESP-GT-POWER</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3977,7 +6263,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT speed coastdown after breaker open</t>
+          <t xml:space="preserve">GT power response after breaker open</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3992,12 +6278,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52GT opens, speed decays from nominal by coastdown model</t>
+          <t xml:space="preserve">if 52GT not closed then GT generator power = 0</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dynamic</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4007,7 +6293,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTGSpeedRPM</t>
+          <t xml:space="preserve">vppGTGPowerMW</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4028,23 +6314,68 @@
       <c r="M50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Exact model equation</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+          <t xml:space="preserve">RESP-GT-SPEED</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Response</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST grid power response after 52ST opens</t>
+          <t xml:space="preserve">GT speed coastdown after breaker open</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4054,27 +6385,27 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
+          <t xml:space="preserve">if 52GT opens, speed decays from nominal by coastdown model</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">immediate model relation</t>
+          <t xml:space="preserve">dynamic</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">follows 52ST closed feedback</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTGridPowerMW</t>
+          <t xml:space="preserve">vppGTGSpeedRPM</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4084,64 +6415,109 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-036</t>
+          <t xml:space="preserve">IG-029</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exact Modelica equation + private local RAW readback hash; behavior verification remains PARTIAL</t>
+          <t xml:space="preserve">Exact model equation</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-OPEN</t>
+          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT Protection</t>
+          <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT breaker open timing</t>
+          <t xml:space="preserve">ST grid power response after 52ST opens</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+          <t xml:space="preserve">PHYSICAL_RESPONSE</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
+          <t xml:space="preserve">vppSTGeneratorPowerMW | vpp52STClosed</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">vppSTGridPowerMW = if not vpp52STClosed then 0 else vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.080 s</t>
+          <t xml:space="preserve">immediate model relation</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">follows 52ST closed feedback</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTClosed</t>
+          <t xml:space="preserve">vppSTGridPowerMW</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4151,7 +6527,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-026</t>
+          <t xml:space="preserve">IG-036</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4161,14 +6537,59 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+          <t xml:space="preserve">Model source modelica/TripLens_CombinedCycle_TripTAC_ProcessView_v36.mo lines 1136-1137 (cd454995656af9a8747efe8930d2aa0b92f98e1083acadc858eaa7959ea6d2c5); RAW RAW_SESSION_20260924_191347.csv (055f8a21b8f586feafaa6fe6705cfca05b4f1e833713991a0cac1f0e94ad6fd9).; 2026-09-26 PlantControlV2 104046 runtime proof verified 52ST OPEN -&gt; vppSTGridPowerMW = 0 MW.</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_RAW_OBSERVED</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MODEL_SOURCE_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_RUNTIME_VERIFIED</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUNTIME_VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
+          <t xml:space="preserve">SEQ-52GT-OPEN</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4178,7 +6599,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52GT trip command timing</t>
+          <t xml:space="preserve">52GT breaker open timing</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4188,17 +6609,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripLatch</t>
+          <t xml:space="preserve">vppGTTripLatch | vppECMS52GTClosedCommandNative</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GT latch active</t>
+          <t xml:space="preserve">GT latch active -&gt; breaker opens</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.055 s</t>
+          <t xml:space="preserve">0.080 s</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4208,7 +6629,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52GTTripCmd</t>
+          <t xml:space="preserve">vpp52GTClosed</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4218,7 +6639,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-025</t>
+          <t xml:space="preserve">IG-026</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4228,24 +6649,69 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+          <t xml:space="preserve">vppGTBreakerOpenDelay = 0.080 s; EVENT run observed 48.44 -&gt; 48.520005</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52GT-TRIPCMD</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST Protection</t>
+          <t xml:space="preserve">GT Protection</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52GT trip command timing</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4255,17 +6721,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppGTTripLatch</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">GT latch active</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0.055 s</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4275,7 +6741,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52GTTripCmd</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4285,7 +6751,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-025</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4295,79 +6761,281 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+          <t xml:space="preserve">vppGTTripCommandDelay = 0.055 s</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST Protection</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52ST breaker open timing</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BREAKER_SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpp52STClosed</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_NODE</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-028</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppSTBreakerOpenDelay = 0.100 s; EVENT run observed 48.44 -&gt; 48.540005</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST Protection</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BREAKER_SEQUENCE</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">0 s</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RAW_NODE</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IG-027</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Runtime node sequence</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_OPCUA_CENSUS</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIVE_RUNTIME</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:V56"/>
 </worksheet>
 </file>
 
@@ -5094,7 +7762,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppCauseDirectGTTrip | vppCauseDirectSTTrip | vppCauseGTBreakerOpenWhileRunning | vppCauseHPDrumHH | vppCauseHPDrumLL | vppCauseIPDrumHH | vppCauseIPDrumLL | vppCauseLPDrumHH | vppCauseLPDrumLL</t>
+          <t xml:space="preserve">vppCauseDirectSTTrip | vppCauseHPDrumHH | vppCauseIPDrumHH | vppCauseLPDrumHH | vppCauseSTBreakerOpenWhileRunning | vppGTTripRequest</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5542,7 +8210,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52STClosed | vppSTGeneratorPowerMW</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5566,8 +8234,40 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROT-ST-BRK-OPEN</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vppCauseSTBreakerOpenWhileRunning</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IG-037</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F38"/>
 </worksheet>
 </file>
 
@@ -8080,79 +10780,79 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESP-ST-GRID-POWER</t>
+          <t xml:space="preserve">SEQ-52ST-OPEN</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-036</t>
+          <t xml:space="preserve">IG-028</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST grid power response after 52ST opens</t>
+          <t xml:space="preserve">52ST breaker open timing</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.100 s</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">vpp52STClosed</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">if 52ST not closed then ST grid power = 0; otherwise ST grid power = ST generator power</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">immediate model relation</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">follows 52ST closed feedback</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vppSTGridPowerMW</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEQ-52ST-OPEN</t>
+          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IG-028</t>
+          <t xml:space="preserve">IG-027</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52ST breaker open timing</t>
+          <t xml:space="preserve">52ST trip command</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vppSTTripLatchPublished | vppECMS52STClosedCommandNative</t>
+          <t xml:space="preserve">vppSTTripLatchPublished</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST latch active -&gt; breaker opens</t>
+          <t xml:space="preserve">ST latch active</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.100 s</t>
+          <t xml:space="preserve">0 s</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8162,7 +10862,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpp52STClosed</t>
+          <t xml:space="preserve">vpp52STTripCmd</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8171,54 +10871,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEQ-52ST-TRIPCMD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IG-027</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52ST trip command</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vppSTTripLatchPublished</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST latch active</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 s</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpp52STTripCmd</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:I6"/>
 </worksheet>
 </file>